--- a/templates/template_developmental_brainage.xlsx
+++ b/templates/template_developmental_brainage.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordan/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68600ED-7E51-8D4A-870E-E6413F002A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Am+jtKa0D/Wzc4IvxFmfRUDjvXYE2QIwHPQFrMCEdMw="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="802">
   <si>
     <t>AGE</t>
   </si>
@@ -2419,28 +2428,41 @@
   </si>
   <si>
     <t>X7Networks_RH_Default_pCunPCC_9area</t>
+  </si>
+  <si>
+    <t>SubjectID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2448,37 +2470,45 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2668,3427 +2698,3428 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:ADV1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="801" width="10.56"/>
+    <col min="2" max="802" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BF1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BH1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BI1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BK1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BL1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BM1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BN1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BO1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BP1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BR1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BS1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BT1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BU1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BV1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BW1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BX1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BY1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="CA1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CB1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CC1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CD1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CE1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CF1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CG1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CH1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CI1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CK1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CL1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CM1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CN1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CO1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CP1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CR1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="2" t="s">
+      <c r="CS1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CT1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CU1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CV1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CW1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CX1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CY1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CZ1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" s="2" t="s">
+      <c r="DA1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DB1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DC1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DD1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DE1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DF1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DG1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DH1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DI1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DJ1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="DJ1" s="2" t="s">
+      <c r="DK1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="DK1" s="2" t="s">
+      <c r="DL1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="DL1" s="2" t="s">
+      <c r="DM1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="DM1" s="2" t="s">
+      <c r="DN1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="DN1" s="2" t="s">
+      <c r="DO1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="DO1" s="2" t="s">
+      <c r="DP1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="DP1" s="2" t="s">
+      <c r="DQ1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="DQ1" s="2" t="s">
+      <c r="DR1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="DR1" s="2" t="s">
+      <c r="DS1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="DS1" s="2" t="s">
+      <c r="DT1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="DT1" s="2" t="s">
+      <c r="DU1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="DU1" s="2" t="s">
+      <c r="DV1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="DV1" s="2" t="s">
+      <c r="DW1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="DW1" s="2" t="s">
+      <c r="DX1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="DX1" s="2" t="s">
+      <c r="DY1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="DY1" s="2" t="s">
+      <c r="DZ1" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="DZ1" s="2" t="s">
+      <c r="EA1" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="EA1" s="2" t="s">
+      <c r="EB1" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="EB1" s="2" t="s">
+      <c r="EC1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="EC1" s="2" t="s">
+      <c r="ED1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="ED1" s="2" t="s">
+      <c r="EE1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="EE1" s="2" t="s">
+      <c r="EF1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="EF1" s="2" t="s">
+      <c r="EG1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="EG1" s="2" t="s">
+      <c r="EH1" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="EH1" s="2" t="s">
+      <c r="EI1" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="EI1" s="2" t="s">
+      <c r="EJ1" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="EJ1" s="2" t="s">
+      <c r="EK1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="EK1" s="2" t="s">
+      <c r="EL1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="EL1" s="2" t="s">
+      <c r="EM1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="EM1" s="2" t="s">
+      <c r="EN1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="EN1" s="2" t="s">
+      <c r="EO1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="EO1" s="2" t="s">
+      <c r="EP1" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="EP1" s="2" t="s">
+      <c r="EQ1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="EQ1" s="2" t="s">
+      <c r="ER1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="ER1" s="2" t="s">
+      <c r="ES1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="ES1" s="2" t="s">
+      <c r="ET1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="ET1" s="2" t="s">
+      <c r="EU1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="EU1" s="2" t="s">
+      <c r="EV1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="EV1" s="2" t="s">
+      <c r="EW1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="EW1" s="2" t="s">
+      <c r="EX1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="EX1" s="2" t="s">
+      <c r="EY1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="EY1" s="2" t="s">
+      <c r="EZ1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="EZ1" s="2" t="s">
+      <c r="FA1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="FA1" s="2" t="s">
+      <c r="FB1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="FB1" s="2" t="s">
+      <c r="FC1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="FC1" s="2" t="s">
+      <c r="FD1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="FD1" s="2" t="s">
+      <c r="FE1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="FE1" s="2" t="s">
+      <c r="FF1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="FF1" s="2" t="s">
+      <c r="FG1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="FG1" s="2" t="s">
+      <c r="FH1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="FH1" s="2" t="s">
+      <c r="FI1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="FI1" s="2" t="s">
+      <c r="FJ1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="FJ1" s="2" t="s">
+      <c r="FK1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="FK1" s="2" t="s">
+      <c r="FL1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="FL1" s="2" t="s">
+      <c r="FM1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="FM1" s="2" t="s">
+      <c r="FN1" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="FN1" s="2" t="s">
+      <c r="FO1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="FO1" s="2" t="s">
+      <c r="FP1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="FP1" s="2" t="s">
+      <c r="FQ1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="FQ1" s="2" t="s">
+      <c r="FR1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="FR1" s="2" t="s">
+      <c r="FS1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="FS1" s="2" t="s">
+      <c r="FT1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="FT1" s="2" t="s">
+      <c r="FU1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="FU1" s="2" t="s">
+      <c r="FV1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="FV1" s="2" t="s">
+      <c r="FW1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="FW1" s="2" t="s">
+      <c r="FX1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="FX1" s="2" t="s">
+      <c r="FY1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="FY1" s="2" t="s">
+      <c r="FZ1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="FZ1" s="2" t="s">
+      <c r="GA1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="GA1" s="2" t="s">
+      <c r="GB1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="GB1" s="2" t="s">
+      <c r="GC1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="GC1" s="2" t="s">
+      <c r="GD1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="GD1" s="2" t="s">
+      <c r="GE1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="GE1" s="2" t="s">
+      <c r="GF1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="GF1" s="2" t="s">
+      <c r="GG1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="GG1" s="2" t="s">
+      <c r="GH1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="GH1" s="2" t="s">
+      <c r="GI1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="GI1" s="2" t="s">
+      <c r="GJ1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="GJ1" s="2" t="s">
+      <c r="GK1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="GK1" s="2" t="s">
+      <c r="GL1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="GL1" s="2" t="s">
+      <c r="GM1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="GM1" s="2" t="s">
+      <c r="GN1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="GN1" s="2" t="s">
+      <c r="GO1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="GO1" s="2" t="s">
+      <c r="GP1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="GP1" s="2" t="s">
+      <c r="GQ1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="GQ1" s="2" t="s">
+      <c r="GR1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="GR1" s="2" t="s">
+      <c r="GS1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="GS1" s="2" t="s">
+      <c r="GT1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="GT1" s="2" t="s">
+      <c r="GU1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="GU1" s="2" t="s">
+      <c r="GV1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="GV1" s="2" t="s">
+      <c r="GW1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="GW1" s="2" t="s">
+      <c r="GX1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="GX1" s="2" t="s">
+      <c r="GY1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="GY1" s="2" t="s">
+      <c r="GZ1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="GZ1" s="2" t="s">
+      <c r="HA1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="HA1" s="2" t="s">
+      <c r="HB1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="HB1" s="2" t="s">
+      <c r="HC1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="HC1" s="2" t="s">
+      <c r="HD1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="HD1" s="2" t="s">
+      <c r="HE1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="HE1" s="2" t="s">
+      <c r="HF1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="HF1" s="2" t="s">
+      <c r="HG1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="HG1" s="2" t="s">
+      <c r="HH1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="HH1" s="2" t="s">
+      <c r="HI1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="HI1" s="2" t="s">
+      <c r="HJ1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="HJ1" s="2" t="s">
+      <c r="HK1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="HK1" s="2" t="s">
+      <c r="HL1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="HL1" s="2" t="s">
+      <c r="HM1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="HM1" s="2" t="s">
+      <c r="HN1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="HN1" s="2" t="s">
+      <c r="HO1" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="HO1" s="2" t="s">
+      <c r="HP1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="HP1" s="2" t="s">
+      <c r="HQ1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="HQ1" s="2" t="s">
+      <c r="HR1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="HR1" s="2" t="s">
+      <c r="HS1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="HS1" s="2" t="s">
+      <c r="HT1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="HT1" s="2" t="s">
+      <c r="HU1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="HU1" s="2" t="s">
+      <c r="HV1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="HV1" s="2" t="s">
+      <c r="HW1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="HW1" s="2" t="s">
+      <c r="HX1" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="HX1" s="2" t="s">
+      <c r="HY1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="HY1" s="2" t="s">
+      <c r="HZ1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="HZ1" s="2" t="s">
+      <c r="IA1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="IA1" s="2" t="s">
+      <c r="IB1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="IB1" s="2" t="s">
+      <c r="IC1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="IC1" s="2" t="s">
+      <c r="ID1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="ID1" s="2" t="s">
+      <c r="IE1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="IE1" s="2" t="s">
+      <c r="IF1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="IF1" s="2" t="s">
+      <c r="IG1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="IG1" s="2" t="s">
+      <c r="IH1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="IH1" s="2" t="s">
+      <c r="II1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="II1" s="2" t="s">
+      <c r="IJ1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="IJ1" s="2" t="s">
+      <c r="IK1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="IK1" s="2" t="s">
+      <c r="IL1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="IL1" s="2" t="s">
+      <c r="IM1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="IM1" s="2" t="s">
+      <c r="IN1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="IN1" s="2" t="s">
+      <c r="IO1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="IO1" s="2" t="s">
+      <c r="IP1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="IP1" s="2" t="s">
+      <c r="IQ1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="IQ1" s="2" t="s">
+      <c r="IR1" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="IR1" s="2" t="s">
+      <c r="IS1" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="IS1" s="2" t="s">
+      <c r="IT1" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="IT1" s="2" t="s">
+      <c r="IU1" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="IU1" s="2" t="s">
+      <c r="IV1" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="IV1" s="2" t="s">
+      <c r="IW1" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="IW1" s="2" t="s">
+      <c r="IX1" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="IX1" s="2" t="s">
+      <c r="IY1" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="IY1" s="2" t="s">
+      <c r="IZ1" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="IZ1" s="2" t="s">
+      <c r="JA1" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="JA1" s="2" t="s">
+      <c r="JB1" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="JB1" s="2" t="s">
+      <c r="JC1" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="JC1" s="2" t="s">
+      <c r="JD1" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="JD1" s="2" t="s">
+      <c r="JE1" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="JE1" s="2" t="s">
+      <c r="JF1" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="JF1" s="2" t="s">
+      <c r="JG1" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="JG1" s="2" t="s">
+      <c r="JH1" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="JH1" s="2" t="s">
+      <c r="JI1" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="JI1" s="2" t="s">
+      <c r="JJ1" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="JJ1" s="2" t="s">
+      <c r="JK1" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="JK1" s="2" t="s">
+      <c r="JL1" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="JL1" s="2" t="s">
+      <c r="JM1" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="JM1" s="2" t="s">
+      <c r="JN1" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="JN1" s="2" t="s">
+      <c r="JO1" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="JO1" s="2" t="s">
+      <c r="JP1" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="JP1" s="2" t="s">
+      <c r="JQ1" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="JQ1" s="2" t="s">
+      <c r="JR1" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="JR1" s="2" t="s">
+      <c r="JS1" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="JS1" s="2" t="s">
+      <c r="JT1" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="JT1" s="2" t="s">
+      <c r="JU1" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="JU1" s="2" t="s">
+      <c r="JV1" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="JV1" s="2" t="s">
+      <c r="JW1" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="JW1" s="2" t="s">
+      <c r="JX1" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="JX1" s="2" t="s">
+      <c r="JY1" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="JY1" s="2" t="s">
+      <c r="JZ1" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="JZ1" s="2" t="s">
+      <c r="KA1" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="KA1" s="2" t="s">
+      <c r="KB1" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="KB1" s="2" t="s">
+      <c r="KC1" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="KC1" s="2" t="s">
+      <c r="KD1" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="KD1" s="2" t="s">
+      <c r="KE1" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="KE1" s="2" t="s">
+      <c r="KF1" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="KF1" s="2" t="s">
+      <c r="KG1" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="KG1" s="2" t="s">
+      <c r="KH1" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="KH1" s="2" t="s">
+      <c r="KI1" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="KI1" s="2" t="s">
+      <c r="KJ1" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="KJ1" s="2" t="s">
+      <c r="KK1" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="KK1" s="2" t="s">
+      <c r="KL1" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="KL1" s="2" t="s">
+      <c r="KM1" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="KM1" s="2" t="s">
+      <c r="KN1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="KN1" s="2" t="s">
+      <c r="KO1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="KO1" s="2" t="s">
+      <c r="KP1" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="KP1" s="2" t="s">
+      <c r="KQ1" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="KQ1" s="2" t="s">
+      <c r="KR1" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="KR1" s="2" t="s">
+      <c r="KS1" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="KS1" s="2" t="s">
+      <c r="KT1" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="KT1" s="2" t="s">
+      <c r="KU1" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="KU1" s="2" t="s">
+      <c r="KV1" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="KV1" s="2" t="s">
+      <c r="KW1" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="KW1" s="2" t="s">
+      <c r="KX1" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="KX1" s="2" t="s">
+      <c r="KY1" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="KY1" s="2" t="s">
+      <c r="KZ1" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="KZ1" s="2" t="s">
+      <c r="LA1" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="LA1" s="2" t="s">
+      <c r="LB1" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="LB1" s="2" t="s">
+      <c r="LC1" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="LC1" s="2" t="s">
+      <c r="LD1" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="LD1" s="2" t="s">
+      <c r="LE1" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="LE1" s="2" t="s">
+      <c r="LF1" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="LF1" s="2" t="s">
+      <c r="LG1" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="LG1" s="2" t="s">
+      <c r="LH1" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="LH1" s="2" t="s">
+      <c r="LI1" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="LI1" s="2" t="s">
+      <c r="LJ1" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="LJ1" s="2" t="s">
+      <c r="LK1" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="LK1" s="2" t="s">
+      <c r="LL1" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="LL1" s="2" t="s">
+      <c r="LM1" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="LM1" s="2" t="s">
+      <c r="LN1" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="LN1" s="2" t="s">
+      <c r="LO1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="LO1" s="2" t="s">
+      <c r="LP1" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="LP1" s="2" t="s">
+      <c r="LQ1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="LQ1" s="2" t="s">
+      <c r="LR1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="LR1" s="2" t="s">
+      <c r="LS1" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="LS1" s="2" t="s">
+      <c r="LT1" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="LT1" s="2" t="s">
+      <c r="LU1" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="LU1" s="2" t="s">
+      <c r="LV1" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="LV1" s="2" t="s">
+      <c r="LW1" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="LW1" s="2" t="s">
+      <c r="LX1" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="LX1" s="2" t="s">
+      <c r="LY1" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="LY1" s="2" t="s">
+      <c r="LZ1" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="LZ1" s="2" t="s">
+      <c r="MA1" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="MA1" s="2" t="s">
+      <c r="MB1" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="MB1" s="2" t="s">
+      <c r="MC1" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="MC1" s="2" t="s">
+      <c r="MD1" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="MD1" s="2" t="s">
+      <c r="ME1" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="ME1" s="2" t="s">
+      <c r="MF1" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="MF1" s="2" t="s">
+      <c r="MG1" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="MG1" s="2" t="s">
+      <c r="MH1" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="MH1" s="2" t="s">
+      <c r="MI1" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="MI1" s="2" t="s">
+      <c r="MJ1" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="MJ1" s="2" t="s">
+      <c r="MK1" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="MK1" s="2" t="s">
+      <c r="ML1" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="ML1" s="2" t="s">
+      <c r="MM1" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="MM1" s="2" t="s">
+      <c r="MN1" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="MN1" s="2" t="s">
+      <c r="MO1" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="MO1" s="2" t="s">
+      <c r="MP1" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="MP1" s="2" t="s">
+      <c r="MQ1" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="MQ1" s="2" t="s">
+      <c r="MR1" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="MR1" s="2" t="s">
+      <c r="MS1" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="MS1" s="2" t="s">
+      <c r="MT1" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="MT1" s="2" t="s">
+      <c r="MU1" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="MU1" s="2" t="s">
+      <c r="MV1" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="MV1" s="2" t="s">
+      <c r="MW1" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="MW1" s="2" t="s">
+      <c r="MX1" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="MX1" s="2" t="s">
+      <c r="MY1" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="MY1" s="2" t="s">
+      <c r="MZ1" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="MZ1" s="2" t="s">
+      <c r="NA1" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="NA1" s="2" t="s">
+      <c r="NB1" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="NB1" s="2" t="s">
+      <c r="NC1" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="NC1" s="2" t="s">
+      <c r="ND1" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="ND1" s="2" t="s">
+      <c r="NE1" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="NE1" s="2" t="s">
+      <c r="NF1" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="NF1" s="2" t="s">
+      <c r="NG1" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="NG1" s="2" t="s">
+      <c r="NH1" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="NH1" s="2" t="s">
+      <c r="NI1" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="NI1" s="2" t="s">
+      <c r="NJ1" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="NJ1" s="2" t="s">
+      <c r="NK1" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="NK1" s="2" t="s">
+      <c r="NL1" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="NL1" s="2" t="s">
+      <c r="NM1" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="NM1" s="2" t="s">
+      <c r="NN1" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="NN1" s="2" t="s">
+      <c r="NO1" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="NO1" s="2" t="s">
+      <c r="NP1" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="NP1" s="2" t="s">
+      <c r="NQ1" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="NQ1" s="2" t="s">
+      <c r="NR1" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="NR1" s="2" t="s">
+      <c r="NS1" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="NS1" s="2" t="s">
+      <c r="NT1" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="NT1" s="2" t="s">
+      <c r="NU1" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="NU1" s="2" t="s">
+      <c r="NV1" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="NV1" s="2" t="s">
+      <c r="NW1" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="NW1" s="2" t="s">
+      <c r="NX1" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="NX1" s="2" t="s">
+      <c r="NY1" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="NY1" s="2" t="s">
+      <c r="NZ1" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="NZ1" s="2" t="s">
+      <c r="OA1" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="OA1" s="2" t="s">
+      <c r="OB1" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="OB1" s="2" t="s">
+      <c r="OC1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="OC1" s="2" t="s">
+      <c r="OD1" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="OD1" s="2" t="s">
+      <c r="OE1" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="OE1" s="2" t="s">
+      <c r="OF1" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="OF1" s="2" t="s">
+      <c r="OG1" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="OG1" s="2" t="s">
+      <c r="OH1" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="OH1" s="2" t="s">
+      <c r="OI1" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="OI1" s="2" t="s">
+      <c r="OJ1" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="OJ1" s="2" t="s">
+      <c r="OK1" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="OK1" s="2" t="s">
+      <c r="OL1" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="OL1" s="2" t="s">
+      <c r="OM1" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="OM1" s="2" t="s">
+      <c r="ON1" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="ON1" s="2" t="s">
+      <c r="OO1" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="OO1" s="2" t="s">
+      <c r="OP1" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="OP1" s="2" t="s">
+      <c r="OQ1" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="OQ1" s="2" t="s">
+      <c r="OR1" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="OR1" s="2" t="s">
+      <c r="OS1" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="OS1" s="2" t="s">
+      <c r="OT1" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="OT1" s="2" t="s">
+      <c r="OU1" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="OU1" s="2" t="s">
+      <c r="OV1" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="OV1" s="2" t="s">
+      <c r="OW1" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="OW1" s="2" t="s">
+      <c r="OX1" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="OX1" s="2" t="s">
+      <c r="OY1" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="OY1" s="2" t="s">
+      <c r="OZ1" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="OZ1" s="2" t="s">
+      <c r="PA1" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="PA1" s="2" t="s">
+      <c r="PB1" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="PB1" s="2" t="s">
+      <c r="PC1" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="PC1" s="2" t="s">
+      <c r="PD1" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="PD1" s="2" t="s">
+      <c r="PE1" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="PE1" s="2" t="s">
+      <c r="PF1" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="PF1" s="2" t="s">
+      <c r="PG1" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="PG1" s="2" t="s">
+      <c r="PH1" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="PH1" s="2" t="s">
+      <c r="PI1" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="PI1" s="2" t="s">
+      <c r="PJ1" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="PJ1" s="2" t="s">
+      <c r="PK1" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="PK1" s="2" t="s">
+      <c r="PL1" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="PL1" s="2" t="s">
+      <c r="PM1" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="PM1" s="2" t="s">
+      <c r="PN1" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="PN1" s="2" t="s">
+      <c r="PO1" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="PO1" s="2" t="s">
+      <c r="PP1" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="PP1" s="2" t="s">
+      <c r="PQ1" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="PQ1" s="2" t="s">
+      <c r="PR1" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="PR1" s="2" t="s">
+      <c r="PS1" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="PS1" s="2" t="s">
+      <c r="PT1" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="PT1" s="2" t="s">
+      <c r="PU1" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="PU1" s="2" t="s">
+      <c r="PV1" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="PV1" s="2" t="s">
+      <c r="PW1" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="PW1" s="2" t="s">
+      <c r="PX1" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="PX1" s="2" t="s">
+      <c r="PY1" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="PY1" s="2" t="s">
+      <c r="PZ1" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="PZ1" s="2" t="s">
+      <c r="QA1" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="QA1" s="2" t="s">
+      <c r="QB1" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="QB1" s="2" t="s">
+      <c r="QC1" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="QC1" s="2" t="s">
+      <c r="QD1" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="QD1" s="2" t="s">
+      <c r="QE1" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="QE1" s="2" t="s">
+      <c r="QF1" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="QF1" s="2" t="s">
+      <c r="QG1" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="QG1" s="2" t="s">
+      <c r="QH1" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="QH1" s="2" t="s">
+      <c r="QI1" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="QI1" s="2" t="s">
+      <c r="QJ1" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="QJ1" s="2" t="s">
+      <c r="QK1" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="QK1" s="2" t="s">
+      <c r="QL1" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="QL1" s="2" t="s">
+      <c r="QM1" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="QM1" s="2" t="s">
+      <c r="QN1" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="QN1" s="2" t="s">
+      <c r="QO1" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="QO1" s="2" t="s">
+      <c r="QP1" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="QP1" s="2" t="s">
+      <c r="QQ1" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="QQ1" s="2" t="s">
+      <c r="QR1" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="QR1" s="2" t="s">
+      <c r="QS1" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="QS1" s="2" t="s">
+      <c r="QT1" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="QT1" s="2" t="s">
+      <c r="QU1" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="QU1" s="2" t="s">
+      <c r="QV1" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="QV1" s="2" t="s">
+      <c r="QW1" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="QW1" s="2" t="s">
+      <c r="QX1" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="QX1" s="2" t="s">
+      <c r="QY1" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="QY1" s="2" t="s">
+      <c r="QZ1" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="QZ1" s="2" t="s">
+      <c r="RA1" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="RA1" s="2" t="s">
+      <c r="RB1" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="RB1" s="2" t="s">
+      <c r="RC1" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="RC1" s="2" t="s">
+      <c r="RD1" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="RD1" s="2" t="s">
+      <c r="RE1" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="RE1" s="2" t="s">
+      <c r="RF1" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="RF1" s="2" t="s">
+      <c r="RG1" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="RG1" s="2" t="s">
+      <c r="RH1" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="RH1" s="2" t="s">
+      <c r="RI1" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="RI1" s="2" t="s">
+      <c r="RJ1" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="RJ1" s="2" t="s">
+      <c r="RK1" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="RK1" s="2" t="s">
+      <c r="RL1" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="RL1" s="2" t="s">
+      <c r="RM1" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="RM1" s="2" t="s">
+      <c r="RN1" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="RN1" s="2" t="s">
+      <c r="RO1" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="RO1" s="2" t="s">
+      <c r="RP1" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="RP1" s="2" t="s">
+      <c r="RQ1" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="RQ1" s="2" t="s">
+      <c r="RR1" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="RR1" s="2" t="s">
+      <c r="RS1" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="RS1" s="2" t="s">
+      <c r="RT1" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="RT1" s="2" t="s">
+      <c r="RU1" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="RU1" s="2" t="s">
+      <c r="RV1" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="RV1" s="2" t="s">
+      <c r="RW1" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="RW1" s="2" t="s">
+      <c r="RX1" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="RX1" s="2" t="s">
+      <c r="RY1" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="RY1" s="2" t="s">
+      <c r="RZ1" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="RZ1" s="2" t="s">
+      <c r="SA1" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="SA1" s="2" t="s">
+      <c r="SB1" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="SB1" s="2" t="s">
+      <c r="SC1" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="SC1" s="2" t="s">
+      <c r="SD1" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="SD1" s="2" t="s">
+      <c r="SE1" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="SE1" s="2" t="s">
+      <c r="SF1" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="SF1" s="2" t="s">
+      <c r="SG1" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="SG1" s="2" t="s">
+      <c r="SH1" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="SH1" s="2" t="s">
+      <c r="SI1" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="SI1" s="2" t="s">
+      <c r="SJ1" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="SJ1" s="2" t="s">
+      <c r="SK1" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="SK1" s="2" t="s">
+      <c r="SL1" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="SL1" s="2" t="s">
+      <c r="SM1" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="SM1" s="2" t="s">
+      <c r="SN1" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="SN1" s="2" t="s">
+      <c r="SO1" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="SO1" s="2" t="s">
+      <c r="SP1" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="SP1" s="2" t="s">
+      <c r="SQ1" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="SQ1" s="2" t="s">
+      <c r="SR1" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="SR1" s="2" t="s">
+      <c r="SS1" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="SS1" s="2" t="s">
+      <c r="ST1" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="ST1" s="2" t="s">
+      <c r="SU1" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="SU1" s="2" t="s">
+      <c r="SV1" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="SV1" s="2" t="s">
+      <c r="SW1" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="SW1" s="2" t="s">
+      <c r="SX1" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="SX1" s="2" t="s">
+      <c r="SY1" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="SY1" s="2" t="s">
+      <c r="SZ1" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="SZ1" s="2" t="s">
+      <c r="TA1" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="TA1" s="2" t="s">
+      <c r="TB1" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="TB1" s="2" t="s">
+      <c r="TC1" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="TC1" s="2" t="s">
+      <c r="TD1" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="TD1" s="2" t="s">
+      <c r="TE1" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="TE1" s="2" t="s">
+      <c r="TF1" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="TF1" s="2" t="s">
+      <c r="TG1" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="TG1" s="2" t="s">
+      <c r="TH1" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="TH1" s="2" t="s">
+      <c r="TI1" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="TI1" s="2" t="s">
+      <c r="TJ1" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="TJ1" s="2" t="s">
+      <c r="TK1" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="TK1" s="2" t="s">
+      <c r="TL1" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="TL1" s="2" t="s">
+      <c r="TM1" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="TM1" s="2" t="s">
+      <c r="TN1" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="TN1" s="2" t="s">
+      <c r="TO1" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="TO1" s="2" t="s">
+      <c r="TP1" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="TP1" s="2" t="s">
+      <c r="TQ1" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="TQ1" s="2" t="s">
+      <c r="TR1" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="TR1" s="2" t="s">
+      <c r="TS1" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="TS1" s="2" t="s">
+      <c r="TT1" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="TT1" s="2" t="s">
+      <c r="TU1" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="TU1" s="2" t="s">
+      <c r="TV1" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="TV1" s="2" t="s">
+      <c r="TW1" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="TW1" s="2" t="s">
+      <c r="TX1" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="TX1" s="2" t="s">
+      <c r="TY1" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="TY1" s="2" t="s">
+      <c r="TZ1" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="TZ1" s="2" t="s">
+      <c r="UA1" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="UA1" s="2" t="s">
+      <c r="UB1" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="UB1" s="2" t="s">
+      <c r="UC1" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="UC1" s="2" t="s">
+      <c r="UD1" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="UD1" s="2" t="s">
+      <c r="UE1" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="UE1" s="2" t="s">
+      <c r="UF1" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="UF1" s="2" t="s">
+      <c r="UG1" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="UG1" s="2" t="s">
+      <c r="UH1" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="UH1" s="2" t="s">
+      <c r="UI1" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="UI1" s="2" t="s">
+      <c r="UJ1" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="UJ1" s="2" t="s">
+      <c r="UK1" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="UK1" s="2" t="s">
+      <c r="UL1" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="UL1" s="2" t="s">
+      <c r="UM1" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="UM1" s="2" t="s">
+      <c r="UN1" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="UN1" s="2" t="s">
+      <c r="UO1" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="UO1" s="2" t="s">
+      <c r="UP1" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="UP1" s="2" t="s">
+      <c r="UQ1" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="UQ1" s="2" t="s">
+      <c r="UR1" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="UR1" s="2" t="s">
+      <c r="US1" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="US1" s="2" t="s">
+      <c r="UT1" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="UT1" s="2" t="s">
+      <c r="UU1" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="UU1" s="2" t="s">
+      <c r="UV1" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="UV1" s="2" t="s">
+      <c r="UW1" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="UW1" s="2" t="s">
+      <c r="UX1" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="UX1" s="2" t="s">
+      <c r="UY1" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="UY1" s="2" t="s">
+      <c r="UZ1" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="UZ1" s="2" t="s">
+      <c r="VA1" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="VA1" s="2" t="s">
+      <c r="VB1" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="VB1" s="2" t="s">
+      <c r="VC1" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="VC1" s="2" t="s">
+      <c r="VD1" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="VD1" s="2" t="s">
+      <c r="VE1" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="VE1" s="2" t="s">
+      <c r="VF1" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="VF1" s="2" t="s">
+      <c r="VG1" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="VG1" s="2" t="s">
+      <c r="VH1" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="VH1" s="2" t="s">
+      <c r="VI1" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="VI1" s="2" t="s">
+      <c r="VJ1" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="VJ1" s="2" t="s">
+      <c r="VK1" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="VK1" s="2" t="s">
+      <c r="VL1" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="VL1" s="2" t="s">
+      <c r="VM1" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="VM1" s="2" t="s">
+      <c r="VN1" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="VN1" s="2" t="s">
+      <c r="VO1" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="VO1" s="2" t="s">
+      <c r="VP1" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="VP1" s="2" t="s">
+      <c r="VQ1" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="VQ1" s="2" t="s">
+      <c r="VR1" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="VR1" s="2" t="s">
+      <c r="VS1" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="VS1" s="2" t="s">
+      <c r="VT1" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="VT1" s="2" t="s">
+      <c r="VU1" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="VU1" s="2" t="s">
+      <c r="VV1" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="VV1" s="2" t="s">
+      <c r="VW1" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="VW1" s="2" t="s">
+      <c r="VX1" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="VX1" s="2" t="s">
+      <c r="VY1" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="VY1" s="2" t="s">
+      <c r="VZ1" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="VZ1" s="2" t="s">
+      <c r="WA1" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="WA1" s="2" t="s">
+      <c r="WB1" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="WB1" s="2" t="s">
+      <c r="WC1" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="WC1" s="2" t="s">
+      <c r="WD1" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="WD1" s="2" t="s">
+      <c r="WE1" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="WE1" s="2" t="s">
+      <c r="WF1" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="WF1" s="2" t="s">
+      <c r="WG1" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="WG1" s="2" t="s">
+      <c r="WH1" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="WH1" s="2" t="s">
+      <c r="WI1" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="WI1" s="2" t="s">
+      <c r="WJ1" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="WJ1" s="2" t="s">
+      <c r="WK1" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="WK1" s="2" t="s">
+      <c r="WL1" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="WL1" s="2" t="s">
+      <c r="WM1" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="WM1" s="2" t="s">
+      <c r="WN1" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="WN1" s="2" t="s">
+      <c r="WO1" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="WO1" s="2" t="s">
+      <c r="WP1" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="WP1" s="2" t="s">
+      <c r="WQ1" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="WQ1" s="2" t="s">
+      <c r="WR1" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="WR1" s="2" t="s">
+      <c r="WS1" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="WS1" s="2" t="s">
+      <c r="WT1" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="WT1" s="2" t="s">
+      <c r="WU1" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="WU1" s="2" t="s">
+      <c r="WV1" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="WV1" s="2" t="s">
+      <c r="WW1" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="WW1" s="2" t="s">
+      <c r="WX1" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="WX1" s="2" t="s">
+      <c r="WY1" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="WY1" s="2" t="s">
+      <c r="WZ1" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="WZ1" s="2" t="s">
+      <c r="XA1" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="XA1" s="2" t="s">
+      <c r="XB1" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="XB1" s="2" t="s">
+      <c r="XC1" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="XC1" s="2" t="s">
+      <c r="XD1" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="XD1" s="2" t="s">
+      <c r="XE1" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="XE1" s="2" t="s">
+      <c r="XF1" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="XF1" s="2" t="s">
+      <c r="XG1" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="XG1" s="2" t="s">
+      <c r="XH1" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="XH1" s="2" t="s">
+      <c r="XI1" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="XI1" s="2" t="s">
+      <c r="XJ1" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="XJ1" s="2" t="s">
+      <c r="XK1" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="XK1" s="2" t="s">
+      <c r="XL1" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="XL1" s="2" t="s">
+      <c r="XM1" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="XM1" s="2" t="s">
+      <c r="XN1" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="XN1" s="2" t="s">
+      <c r="XO1" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="XO1" s="2" t="s">
+      <c r="XP1" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="XP1" s="2" t="s">
+      <c r="XQ1" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="XQ1" s="2" t="s">
+      <c r="XR1" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="XR1" s="2" t="s">
+      <c r="XS1" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="XS1" s="2" t="s">
+      <c r="XT1" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="XT1" s="2" t="s">
+      <c r="XU1" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="XU1" s="2" t="s">
+      <c r="XV1" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="XV1" s="2" t="s">
+      <c r="XW1" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="XW1" s="2" t="s">
+      <c r="XX1" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="XX1" s="2" t="s">
+      <c r="XY1" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="XY1" s="2" t="s">
+      <c r="XZ1" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="XZ1" s="2" t="s">
+      <c r="YA1" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="YA1" s="2" t="s">
+      <c r="YB1" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="YB1" s="2" t="s">
+      <c r="YC1" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="YC1" s="2" t="s">
+      <c r="YD1" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="YD1" s="2" t="s">
+      <c r="YE1" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="YE1" s="2" t="s">
+      <c r="YF1" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="YF1" s="2" t="s">
+      <c r="YG1" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="YG1" s="2" t="s">
+      <c r="YH1" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="YH1" s="2" t="s">
+      <c r="YI1" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="YI1" s="2" t="s">
+      <c r="YJ1" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="YJ1" s="2" t="s">
+      <c r="YK1" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="YK1" s="2" t="s">
+      <c r="YL1" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="YL1" s="2" t="s">
+      <c r="YM1" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="YM1" s="2" t="s">
+      <c r="YN1" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="YN1" s="2" t="s">
+      <c r="YO1" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="YO1" s="2" t="s">
+      <c r="YP1" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="YP1" s="2" t="s">
+      <c r="YQ1" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="YQ1" s="2" t="s">
+      <c r="YR1" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="YR1" s="2" t="s">
+      <c r="YS1" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="YS1" s="2" t="s">
+      <c r="YT1" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="YT1" s="2" t="s">
+      <c r="YU1" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="YU1" s="2" t="s">
+      <c r="YV1" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="YV1" s="2" t="s">
+      <c r="YW1" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="YW1" s="2" t="s">
+      <c r="YX1" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="YX1" s="2" t="s">
+      <c r="YY1" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="YY1" s="2" t="s">
+      <c r="YZ1" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="YZ1" s="2" t="s">
+      <c r="ZA1" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="ZA1" s="2" t="s">
+      <c r="ZB1" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="ZB1" s="2" t="s">
+      <c r="ZC1" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="ZC1" s="2" t="s">
+      <c r="ZD1" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="ZD1" s="2" t="s">
+      <c r="ZE1" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="ZE1" s="2" t="s">
+      <c r="ZF1" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="ZF1" s="2" t="s">
+      <c r="ZG1" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="ZG1" s="2" t="s">
+      <c r="ZH1" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="ZH1" s="2" t="s">
+      <c r="ZI1" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="ZI1" s="2" t="s">
+      <c r="ZJ1" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="ZJ1" s="2" t="s">
+      <c r="ZK1" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="ZK1" s="2" t="s">
+      <c r="ZL1" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="ZL1" s="2" t="s">
+      <c r="ZM1" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="ZM1" s="2" t="s">
+      <c r="ZN1" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="ZN1" s="2" t="s">
+      <c r="ZO1" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="ZO1" s="2" t="s">
+      <c r="ZP1" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="ZP1" s="2" t="s">
+      <c r="ZQ1" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="ZQ1" s="2" t="s">
+      <c r="ZR1" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="ZR1" s="2" t="s">
+      <c r="ZS1" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="ZS1" s="2" t="s">
+      <c r="ZT1" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="ZT1" s="2" t="s">
+      <c r="ZU1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="ZU1" s="2" t="s">
+      <c r="ZV1" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="ZV1" s="2" t="s">
+      <c r="ZW1" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="ZW1" s="2" t="s">
+      <c r="ZX1" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="ZX1" s="2" t="s">
+      <c r="ZY1" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="ZY1" s="2" t="s">
+      <c r="ZZ1" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="ZZ1" s="2" t="s">
+      <c r="AAA1" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="AAA1" s="2" t="s">
+      <c r="AAB1" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="AAB1" s="2" t="s">
+      <c r="AAC1" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="AAC1" s="2" t="s">
+      <c r="AAD1" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="AAD1" s="2" t="s">
+      <c r="AAE1" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="AAE1" s="2" t="s">
+      <c r="AAF1" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="AAF1" s="2" t="s">
+      <c r="AAG1" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="AAG1" s="2" t="s">
+      <c r="AAH1" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="AAH1" s="2" t="s">
+      <c r="AAI1" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="AAI1" s="2" t="s">
+      <c r="AAJ1" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="AAJ1" s="2" t="s">
+      <c r="AAK1" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="AAK1" s="2" t="s">
+      <c r="AAL1" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="AAL1" s="2" t="s">
+      <c r="AAM1" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="AAM1" s="2" t="s">
+      <c r="AAN1" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="AAN1" s="2" t="s">
+      <c r="AAO1" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="AAO1" s="2" t="s">
+      <c r="AAP1" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="AAP1" s="2" t="s">
+      <c r="AAQ1" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="AAQ1" s="2" t="s">
+      <c r="AAR1" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="AAR1" s="2" t="s">
+      <c r="AAS1" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="AAS1" s="2" t="s">
+      <c r="AAT1" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="AAT1" s="2" t="s">
+      <c r="AAU1" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="AAU1" s="2" t="s">
+      <c r="AAV1" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="AAV1" s="2" t="s">
+      <c r="AAW1" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="AAW1" s="2" t="s">
+      <c r="AAX1" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="AAX1" s="2" t="s">
+      <c r="AAY1" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="AAY1" s="2" t="s">
+      <c r="AAZ1" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="AAZ1" s="2" t="s">
+      <c r="ABA1" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="ABA1" s="2" t="s">
+      <c r="ABB1" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="ABB1" s="2" t="s">
+      <c r="ABC1" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="ABC1" s="2" t="s">
+      <c r="ABD1" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="ABD1" s="2" t="s">
+      <c r="ABE1" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="ABE1" s="2" t="s">
+      <c r="ABF1" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="ABF1" s="2" t="s">
+      <c r="ABG1" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="ABG1" s="2" t="s">
+      <c r="ABH1" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="ABH1" s="2" t="s">
+      <c r="ABI1" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="ABI1" s="2" t="s">
+      <c r="ABJ1" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="ABJ1" s="2" t="s">
+      <c r="ABK1" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="ABK1" s="2" t="s">
+      <c r="ABL1" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="ABL1" s="2" t="s">
+      <c r="ABM1" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="ABM1" s="2" t="s">
+      <c r="ABN1" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="ABN1" s="2" t="s">
+      <c r="ABO1" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="ABO1" s="2" t="s">
+      <c r="ABP1" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="ABP1" s="2" t="s">
+      <c r="ABQ1" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="ABQ1" s="2" t="s">
+      <c r="ABR1" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="ABR1" s="2" t="s">
+      <c r="ABS1" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="ABS1" s="2" t="s">
+      <c r="ABT1" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="ABT1" s="2" t="s">
+      <c r="ABU1" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="ABU1" s="2" t="s">
+      <c r="ABV1" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="ABV1" s="2" t="s">
+      <c r="ABW1" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="ABW1" s="2" t="s">
+      <c r="ABX1" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="ABX1" s="2" t="s">
+      <c r="ABY1" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="ABY1" s="2" t="s">
+      <c r="ABZ1" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="ABZ1" s="2" t="s">
+      <c r="ACA1" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="ACA1" s="2" t="s">
+      <c r="ACB1" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="ACB1" s="2" t="s">
+      <c r="ACC1" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="ACC1" s="2" t="s">
+      <c r="ACD1" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="ACD1" s="2" t="s">
+      <c r="ACE1" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="ACE1" s="2" t="s">
+      <c r="ACF1" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="ACF1" s="2" t="s">
+      <c r="ACG1" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="ACG1" s="2" t="s">
+      <c r="ACH1" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="ACH1" s="2" t="s">
+      <c r="ACI1" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="ACI1" s="2" t="s">
+      <c r="ACJ1" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="ACJ1" s="2" t="s">
+      <c r="ACK1" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="ACK1" s="2" t="s">
+      <c r="ACL1" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="ACL1" s="2" t="s">
+      <c r="ACM1" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="ACM1" s="2" t="s">
+      <c r="ACN1" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="ACN1" s="2" t="s">
+      <c r="ACO1" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="ACO1" s="2" t="s">
+      <c r="ACP1" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="ACP1" s="2" t="s">
+      <c r="ACQ1" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="ACQ1" s="2" t="s">
+      <c r="ACR1" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="ACR1" s="2" t="s">
+      <c r="ACS1" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="ACS1" s="2" t="s">
+      <c r="ACT1" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="ACT1" s="2" t="s">
+      <c r="ACU1" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="ACU1" s="2" t="s">
+      <c r="ACV1" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="ACV1" s="2" t="s">
+      <c r="ACW1" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="ACW1" s="2" t="s">
+      <c r="ACX1" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="ACX1" s="2" t="s">
+      <c r="ACY1" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="ACY1" s="2" t="s">
+      <c r="ACZ1" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="ACZ1" s="2" t="s">
+      <c r="ADA1" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="ADA1" s="2" t="s">
+      <c r="ADB1" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="ADB1" s="2" t="s">
+      <c r="ADC1" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="ADC1" s="2" t="s">
+      <c r="ADD1" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="ADD1" s="2" t="s">
+      <c r="ADE1" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="ADE1" s="2" t="s">
+      <c r="ADF1" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="ADF1" s="2" t="s">
+      <c r="ADG1" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="ADG1" s="2" t="s">
+      <c r="ADH1" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="ADH1" s="2" t="s">
+      <c r="ADI1" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="ADI1" s="2" t="s">
+      <c r="ADJ1" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="ADJ1" s="2" t="s">
+      <c r="ADK1" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="ADK1" s="2" t="s">
+      <c r="ADL1" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="ADL1" s="2" t="s">
+      <c r="ADM1" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="ADM1" s="2" t="s">
+      <c r="ADN1" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="ADN1" s="2" t="s">
+      <c r="ADO1" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="ADO1" s="2" t="s">
+      <c r="ADP1" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="ADP1" s="2" t="s">
+      <c r="ADQ1" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="ADQ1" s="2" t="s">
+      <c r="ADR1" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="ADR1" s="2" t="s">
+      <c r="ADS1" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="ADS1" s="2" t="s">
+      <c r="ADT1" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="ADT1" s="2" t="s">
+      <c r="ADU1" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="ADU1" s="2" t="s">
+      <c r="ADV1" s="2" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="15.75" customHeight="1"/>
-    <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1"/>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="2" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>